--- a/Projects/Project_Teams.xlsx
+++ b/Projects/Project_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6B5803-315D-4CCF-9983-CB15A1C74165}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB7230A-FE69-4F87-9A42-34EE82770420}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{CFFCAC46-098C-4A9A-8C1A-17A7E0413977}"/>
   </bookViews>
@@ -309,7 +309,7 @@
     <t>PetConnect</t>
   </si>
   <si>
-    <t>Finsync</t>
+    <t>FinTrust</t>
   </si>
 </sst>
 </file>
